--- a/BWI/bestwine_output/bestwine_Hungary.xlsx
+++ b/BWI/bestwine_output/bestwine_Hungary.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA222"/>
+  <dimension ref="A1:AA223"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -24066,6 +24066,111 @@
         </is>
       </c>
     </row>
+    <row r="223">
+      <c r="A223" s="2" t="inlineStr">
+        <is>
+          <t>Agria Drink Kft.</t>
+        </is>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>Agria Drink Kft.</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="inlineStr">
+        <is>
+          <t>118789</t>
+        </is>
+      </c>
+      <c r="D223" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E223" s="2" t="inlineStr">
+        <is>
+          <t>Eger</t>
+        </is>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>North Hungary</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="inlineStr">
+        <is>
+          <t>183 Kertész utca</t>
+        </is>
+      </c>
+      <c r="H223" s="2" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>https://agriadrink.hu</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr"/>
+      <c r="K223" s="2" t="inlineStr"/>
+      <c r="L223" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="M223" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N223" s="2" t="inlineStr">
+        <is>
+          <t>agriadrink@agriadrink.hu</t>
+        </is>
+      </c>
+      <c r="O223" s="2" t="inlineStr">
+        <is>
+          <t>+36 36 412 254</t>
+        </is>
+      </c>
+      <c r="P223" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q223" s="2" t="inlineStr">
+        <is>
+          <t>11175724210</t>
+        </is>
+      </c>
+      <c r="R223" s="2" t="inlineStr"/>
+      <c r="S223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/agria.drink.eger/</t>
+        </is>
+      </c>
+      <c r="T223" s="2" t="inlineStr"/>
+      <c r="U223" s="2" t="inlineStr"/>
+      <c r="V223" s="2" t="inlineStr"/>
+      <c r="W223" s="2" t="inlineStr">
+        <is>
+          <t>Robert Hervai</t>
+        </is>
+      </c>
+      <c r="X223" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y223" s="2" t="inlineStr"/>
+      <c r="Z223" s="2" t="inlineStr"/>
+      <c r="AA223" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robert-hervai-566989160</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hungary.xlsx
+++ b/BWI/bestwine_output/bestwine_Hungary.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA223"/>
+  <dimension ref="A1:AA224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -24171,6 +24171,111 @@
         </is>
       </c>
     </row>
+    <row r="224">
+      <c r="A224" s="2" t="inlineStr">
+        <is>
+          <t>Agria Drink Kft.</t>
+        </is>
+      </c>
+      <c r="B224" s="2" t="inlineStr">
+        <is>
+          <t>Agria Drink Kft.</t>
+        </is>
+      </c>
+      <c r="C224" s="2" t="inlineStr">
+        <is>
+          <t>118789</t>
+        </is>
+      </c>
+      <c r="D224" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E224" s="2" t="inlineStr">
+        <is>
+          <t>Eger</t>
+        </is>
+      </c>
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>North Hungary</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="inlineStr">
+        <is>
+          <t>183 Kertész utca</t>
+        </is>
+      </c>
+      <c r="H224" s="2" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>https://agriadrink.hu</t>
+        </is>
+      </c>
+      <c r="J224" s="2" t="inlineStr"/>
+      <c r="K224" s="2" t="inlineStr"/>
+      <c r="L224" s="2" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="M224" s="2" t="inlineStr">
+        <is>
+          <t>null</t>
+        </is>
+      </c>
+      <c r="N224" s="2" t="inlineStr">
+        <is>
+          <t>agriadrink@agriadrink.hu</t>
+        </is>
+      </c>
+      <c r="O224" s="2" t="inlineStr">
+        <is>
+          <t>+36 36 412 254</t>
+        </is>
+      </c>
+      <c r="P224" s="2" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="Q224" s="2" t="inlineStr">
+        <is>
+          <t>11175724210</t>
+        </is>
+      </c>
+      <c r="R224" s="2" t="inlineStr"/>
+      <c r="S224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/agria.drink.eger/</t>
+        </is>
+      </c>
+      <c r="T224" s="2" t="inlineStr"/>
+      <c r="U224" s="2" t="inlineStr"/>
+      <c r="V224" s="2" t="inlineStr"/>
+      <c r="W224" s="2" t="inlineStr">
+        <is>
+          <t>Robert Hervai</t>
+        </is>
+      </c>
+      <c r="X224" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y224" s="2" t="inlineStr"/>
+      <c r="Z224" s="2" t="inlineStr"/>
+      <c r="AA224" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/robert-hervai-566989160</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hungary.xlsx
+++ b/BWI/bestwine_output/bestwine_Hungary.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA224"/>
+  <dimension ref="A1:AA226"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -24276,6 +24276,192 @@
         </is>
       </c>
     </row>
+    <row r="225">
+      <c r="A225" s="2" t="inlineStr">
+        <is>
+          <t>Boragóra Korlátolt Felelosségu Társaság</t>
+        </is>
+      </c>
+      <c r="B225" s="2" t="inlineStr">
+        <is>
+          <t>Boragóra Kft.</t>
+        </is>
+      </c>
+      <c r="C225" s="2" t="inlineStr">
+        <is>
+          <t>167803</t>
+        </is>
+      </c>
+      <c r="D225" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E225" s="2" t="inlineStr">
+        <is>
+          <t>Budaörs</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>Pest Megye</t>
+        </is>
+      </c>
+      <c r="G225" s="2" t="inlineStr">
+        <is>
+          <t>Szabadság út 17.</t>
+        </is>
+      </c>
+      <c r="H225" s="2" t="inlineStr">
+        <is>
+          <t>2040</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>https://boragora.hu</t>
+        </is>
+      </c>
+      <c r="J225" s="2" t="inlineStr"/>
+      <c r="K225" s="2" t="inlineStr"/>
+      <c r="L225" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M225" s="2" t="inlineStr">
+        <is>
+          <t>80682</t>
+        </is>
+      </c>
+      <c r="N225" s="2" t="inlineStr">
+        <is>
+          <t>boragora.budaors@gmail.com</t>
+        </is>
+      </c>
+      <c r="O225" s="2" t="inlineStr"/>
+      <c r="P225" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q225" s="2" t="inlineStr">
+        <is>
+          <t>26691932213</t>
+        </is>
+      </c>
+      <c r="R225" s="2" t="inlineStr"/>
+      <c r="S225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/boragoradunakeszi/</t>
+        </is>
+      </c>
+      <c r="T225" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bor_agora/</t>
+        </is>
+      </c>
+      <c r="U225" s="2" t="inlineStr"/>
+      <c r="V225" s="2" t="inlineStr"/>
+      <c r="W225" s="2" t="inlineStr">
+        <is>
+          <t>Megyeri Bíborka Schmidtné</t>
+        </is>
+      </c>
+      <c r="X225" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y225" s="2" t="inlineStr"/>
+      <c r="Z225" s="2" t="inlineStr"/>
+      <c r="AA225" s="2" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" s="2" t="inlineStr">
+        <is>
+          <t>HEDONÉ Korlátolt Felelosségu Társaság</t>
+        </is>
+      </c>
+      <c r="B226" s="2" t="inlineStr">
+        <is>
+          <t>HEDONÉ Kft.</t>
+        </is>
+      </c>
+      <c r="C226" s="2" t="inlineStr">
+        <is>
+          <t>167795</t>
+        </is>
+      </c>
+      <c r="D226" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E226" s="2" t="inlineStr">
+        <is>
+          <t>Szeged</t>
+        </is>
+      </c>
+      <c r="F226" s="2" t="inlineStr">
+        <is>
+          <t>Csongrád Megye</t>
+        </is>
+      </c>
+      <c r="G226" s="2" t="inlineStr">
+        <is>
+          <t>Szoregi út 44.</t>
+        </is>
+      </c>
+      <c r="H226" s="2" t="inlineStr">
+        <is>
+          <t>6726</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>https://hedonedrink.hu</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr"/>
+      <c r="K226" s="2" t="inlineStr"/>
+      <c r="L226" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M226" s="2" t="inlineStr">
+        <is>
+          <t>49000</t>
+        </is>
+      </c>
+      <c r="N226" s="2" t="inlineStr">
+        <is>
+          <t>info@hedonedrink.hu</t>
+        </is>
+      </c>
+      <c r="O226" s="2" t="inlineStr"/>
+      <c r="P226" s="2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="Q226" s="2" t="inlineStr">
+        <is>
+          <t>32871243206</t>
+        </is>
+      </c>
+      <c r="R226" s="2" t="inlineStr"/>
+      <c r="S226" s="2" t="inlineStr"/>
+      <c r="T226" s="2" t="inlineStr"/>
+      <c r="U226" s="2" t="inlineStr"/>
+      <c r="V226" s="2" t="inlineStr"/>
+      <c r="W226" s="2" t="inlineStr"/>
+      <c r="X226" s="2" t="inlineStr"/>
+      <c r="Y226" s="2" t="inlineStr"/>
+      <c r="Z226" s="2" t="inlineStr"/>
+      <c r="AA226" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hungary.xlsx
+++ b/BWI/bestwine_output/bestwine_Hungary.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA226"/>
+  <dimension ref="A1:AA234"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -24462,6 +24462,826 @@
       <c r="Z226" s="2" t="inlineStr"/>
       <c r="AA226" s="2" t="inlineStr"/>
     </row>
+    <row r="227">
+      <c r="A227" s="2" t="inlineStr">
+        <is>
+          <t>ShopOld Kereskedelmi és Szolgáltató Kft.</t>
+        </is>
+      </c>
+      <c r="B227" s="2" t="inlineStr">
+        <is>
+          <t>ShopOld Kft.</t>
+        </is>
+      </c>
+      <c r="C227" s="2" t="inlineStr">
+        <is>
+          <t>167873</t>
+        </is>
+      </c>
+      <c r="D227" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E227" s="2" t="inlineStr">
+        <is>
+          <t>Szeged</t>
+        </is>
+      </c>
+      <c r="F227" s="2" t="inlineStr">
+        <is>
+          <t>Csongrád Megye</t>
+        </is>
+      </c>
+      <c r="G227" s="2" t="inlineStr">
+        <is>
+          <t>Bérkert utca 50.</t>
+        </is>
+      </c>
+      <c r="H227" s="2" t="inlineStr">
+        <is>
+          <t>6726</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.shopold.hu</t>
+        </is>
+      </c>
+      <c r="J227" s="2" t="inlineStr"/>
+      <c r="K227" s="2" t="inlineStr"/>
+      <c r="L227" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M227" s="2" t="inlineStr">
+        <is>
+          <t>196622</t>
+        </is>
+      </c>
+      <c r="N227" s="2" t="inlineStr">
+        <is>
+          <t>csenkeysinko.andras@gmail.com</t>
+        </is>
+      </c>
+      <c r="O227" s="2" t="inlineStr">
+        <is>
+          <t>+670 410 4350</t>
+        </is>
+      </c>
+      <c r="P227" s="2" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Q227" s="2" t="inlineStr">
+        <is>
+          <t>25172968206</t>
+        </is>
+      </c>
+      <c r="R227" s="2" t="inlineStr"/>
+      <c r="S227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100065185763401&amp;locale=hu_HU</t>
+        </is>
+      </c>
+      <c r="T227" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ligetabc/</t>
+        </is>
+      </c>
+      <c r="U227" s="2" t="inlineStr"/>
+      <c r="V227" s="2" t="inlineStr"/>
+      <c r="W227" s="2" t="inlineStr">
+        <is>
+          <t>Csenkey-Sinkó András</t>
+        </is>
+      </c>
+      <c r="X227" s="2" t="inlineStr">
+        <is>
+          <t>Business Manager</t>
+        </is>
+      </c>
+      <c r="Y227" s="2" t="inlineStr"/>
+      <c r="Z227" s="2" t="inlineStr"/>
+      <c r="AA227" s="2" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" s="2" t="inlineStr">
+        <is>
+          <t>PROSECCO JOURNEY Korlátolt Felelosségu Társaság</t>
+        </is>
+      </c>
+      <c r="B228" s="2" t="inlineStr">
+        <is>
+          <t>PROSECCO JOURNEY Kft.</t>
+        </is>
+      </c>
+      <c r="C228" s="2" t="inlineStr">
+        <is>
+          <t>167841</t>
+        </is>
+      </c>
+      <c r="D228" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E228" s="2" t="inlineStr">
+        <is>
+          <t>Etyek</t>
+        </is>
+      </c>
+      <c r="F228" s="2" t="inlineStr">
+        <is>
+          <t>Fejér Megye</t>
+        </is>
+      </c>
+      <c r="G228" s="2" t="inlineStr">
+        <is>
+          <t>Szabadföld utca 10.</t>
+        </is>
+      </c>
+      <c r="H228" s="2" t="inlineStr">
+        <is>
+          <t>2091</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.proseccojourney.hu</t>
+        </is>
+      </c>
+      <c r="J228" s="2" t="inlineStr"/>
+      <c r="K228" s="2" t="inlineStr"/>
+      <c r="L228" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M228" s="2" t="inlineStr">
+        <is>
+          <t>4031</t>
+        </is>
+      </c>
+      <c r="N228" s="2" t="inlineStr">
+        <is>
+          <t>info@proseccojourney.hu</t>
+        </is>
+      </c>
+      <c r="O228" s="2" t="inlineStr"/>
+      <c r="P228" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q228" s="2" t="inlineStr">
+        <is>
+          <t>32715655207</t>
+        </is>
+      </c>
+      <c r="R228" s="2" t="inlineStr">
+        <is>
+          <t>http://linkedin.com/company/prosecco-journey-hu</t>
+        </is>
+      </c>
+      <c r="S228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61566756742733</t>
+        </is>
+      </c>
+      <c r="T228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/proseccojourney_hu/</t>
+        </is>
+      </c>
+      <c r="U228" s="2" t="inlineStr"/>
+      <c r="V228" s="2" t="inlineStr"/>
+      <c r="W228" s="2" t="inlineStr">
+        <is>
+          <t>Ádám Marton</t>
+        </is>
+      </c>
+      <c r="X228" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y228" s="2" t="inlineStr"/>
+      <c r="Z228" s="2" t="inlineStr"/>
+      <c r="AA228" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/adam-marton-06637a148/</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="2" t="inlineStr">
+        <is>
+          <t>PROSECCO JOURNEY Korlátolt Felelosségu Társaság</t>
+        </is>
+      </c>
+      <c r="B229" s="2" t="inlineStr">
+        <is>
+          <t>PROSECCO JOURNEY Kft.</t>
+        </is>
+      </c>
+      <c r="C229" s="2" t="inlineStr">
+        <is>
+          <t>167841</t>
+        </is>
+      </c>
+      <c r="D229" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E229" s="2" t="inlineStr">
+        <is>
+          <t>Etyek</t>
+        </is>
+      </c>
+      <c r="F229" s="2" t="inlineStr">
+        <is>
+          <t>Fejér Megye</t>
+        </is>
+      </c>
+      <c r="G229" s="2" t="inlineStr">
+        <is>
+          <t>Szabadföld utca 10.</t>
+        </is>
+      </c>
+      <c r="H229" s="2" t="inlineStr">
+        <is>
+          <t>2091</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.proseccojourney.hu</t>
+        </is>
+      </c>
+      <c r="J229" s="2" t="inlineStr"/>
+      <c r="K229" s="2" t="inlineStr"/>
+      <c r="L229" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M229" s="2" t="inlineStr">
+        <is>
+          <t>4031</t>
+        </is>
+      </c>
+      <c r="N229" s="2" t="inlineStr">
+        <is>
+          <t>info@proseccojourney.hu</t>
+        </is>
+      </c>
+      <c r="O229" s="2" t="inlineStr"/>
+      <c r="P229" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q229" s="2" t="inlineStr">
+        <is>
+          <t>32715655207</t>
+        </is>
+      </c>
+      <c r="R229" s="2" t="inlineStr">
+        <is>
+          <t>http://linkedin.com/company/prosecco-journey-hu</t>
+        </is>
+      </c>
+      <c r="S229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61566756742733</t>
+        </is>
+      </c>
+      <c r="T229" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/proseccojourney_hu/</t>
+        </is>
+      </c>
+      <c r="U229" s="2" t="inlineStr"/>
+      <c r="V229" s="2" t="inlineStr"/>
+      <c r="W229" s="2" t="inlineStr">
+        <is>
+          <t>Dóra Gulyás</t>
+        </is>
+      </c>
+      <c r="X229" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y229" s="2" t="inlineStr"/>
+      <c r="Z229" s="2" t="inlineStr"/>
+      <c r="AA229" s="2" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" s="2" t="inlineStr">
+        <is>
+          <t>Borstory Borkommunikációs és Borkereskedelmi Betéti Társaság</t>
+        </is>
+      </c>
+      <c r="B230" s="2" t="inlineStr">
+        <is>
+          <t>Borstory Bt.</t>
+        </is>
+      </c>
+      <c r="C230" s="2" t="inlineStr">
+        <is>
+          <t>167838</t>
+        </is>
+      </c>
+      <c r="D230" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E230" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F230" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>Állás utca 55.</t>
+        </is>
+      </c>
+      <c r="H230" s="2" t="inlineStr">
+        <is>
+          <t>1162</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>https://borstory.hu</t>
+        </is>
+      </c>
+      <c r="J230" s="2" t="inlineStr"/>
+      <c r="K230" s="2" t="inlineStr"/>
+      <c r="L230" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M230" s="2" t="inlineStr">
+        <is>
+          <t>5943</t>
+        </is>
+      </c>
+      <c r="N230" s="2" t="inlineStr">
+        <is>
+          <t>info@borstory.hu</t>
+        </is>
+      </c>
+      <c r="O230" s="2" t="inlineStr"/>
+      <c r="P230" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q230" s="2" t="inlineStr">
+        <is>
+          <t>32637706242</t>
+        </is>
+      </c>
+      <c r="R230" s="2" t="inlineStr"/>
+      <c r="S230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=100085921544939</t>
+        </is>
+      </c>
+      <c r="T230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/borstory/</t>
+        </is>
+      </c>
+      <c r="U230" s="2" t="inlineStr"/>
+      <c r="V230" s="2" t="inlineStr"/>
+      <c r="W230" s="2" t="inlineStr">
+        <is>
+          <t>Máté Sztanev</t>
+        </is>
+      </c>
+      <c r="X230" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y230" s="2" t="inlineStr"/>
+      <c r="Z230" s="2" t="inlineStr"/>
+      <c r="AA230" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/sztanev-m%C3%A1t%C3%A9-8814142b7/</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="2" t="inlineStr">
+        <is>
+          <t>Bor Madár Webshop Korlátolt Felelosségu Társaság</t>
+        </is>
+      </c>
+      <c r="B231" s="2" t="inlineStr">
+        <is>
+          <t>Bor Madár Webshop Kft.</t>
+        </is>
+      </c>
+      <c r="C231" s="2" t="inlineStr">
+        <is>
+          <t>167837</t>
+        </is>
+      </c>
+      <c r="D231" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E231" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F231" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="G231" s="2" t="inlineStr">
+        <is>
+          <t>Péceli út 234.</t>
+        </is>
+      </c>
+      <c r="H231" s="2" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>https://bormadar.hu</t>
+        </is>
+      </c>
+      <c r="J231" s="2" t="inlineStr"/>
+      <c r="K231" s="2" t="inlineStr"/>
+      <c r="L231" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M231" s="2" t="inlineStr">
+        <is>
+          <t>2570</t>
+        </is>
+      </c>
+      <c r="N231" s="2" t="inlineStr">
+        <is>
+          <t>info@bormadar.hu</t>
+        </is>
+      </c>
+      <c r="O231" s="2" t="inlineStr"/>
+      <c r="P231" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q231" s="2" t="inlineStr">
+        <is>
+          <t>32556249242</t>
+        </is>
+      </c>
+      <c r="R231" s="2" t="inlineStr"/>
+      <c r="S231" s="2" t="inlineStr"/>
+      <c r="T231" s="2" t="inlineStr"/>
+      <c r="U231" s="2" t="inlineStr"/>
+      <c r="V231" s="2" t="inlineStr"/>
+      <c r="W231" s="2" t="inlineStr">
+        <is>
+          <t>Bódis Bettina Egyedné</t>
+        </is>
+      </c>
+      <c r="X231" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y231" s="2" t="inlineStr"/>
+      <c r="Z231" s="2" t="inlineStr"/>
+      <c r="AA231" s="2" t="inlineStr"/>
+    </row>
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
+        <is>
+          <t>InnoWine Korlátolt Felelosségu Társaság</t>
+        </is>
+      </c>
+      <c r="B232" s="2" t="inlineStr">
+        <is>
+          <t>InnoWine Kft.</t>
+        </is>
+      </c>
+      <c r="C232" s="2" t="inlineStr">
+        <is>
+          <t>167836</t>
+        </is>
+      </c>
+      <c r="D232" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E232" s="2" t="inlineStr">
+        <is>
+          <t>Nagykovácsi</t>
+        </is>
+      </c>
+      <c r="F232" s="2" t="inlineStr">
+        <is>
+          <t>Pest Megye</t>
+        </is>
+      </c>
+      <c r="G232" s="2" t="inlineStr">
+        <is>
+          <t>Gyöngyvirág utca 7.</t>
+        </is>
+      </c>
+      <c r="H232" s="2" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.innowine.hu</t>
+        </is>
+      </c>
+      <c r="J232" s="2" t="inlineStr"/>
+      <c r="K232" s="2" t="inlineStr"/>
+      <c r="L232" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M232" s="2" t="inlineStr">
+        <is>
+          <t>20142</t>
+        </is>
+      </c>
+      <c r="N232" s="2" t="inlineStr">
+        <is>
+          <t>innowine@innowine.hu</t>
+        </is>
+      </c>
+      <c r="O232" s="2" t="inlineStr"/>
+      <c r="P232" s="2" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="Q232" s="2" t="inlineStr">
+        <is>
+          <t>32139246213</t>
+        </is>
+      </c>
+      <c r="R232" s="2" t="inlineStr"/>
+      <c r="S232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/InnowineBorpatika</t>
+        </is>
+      </c>
+      <c r="T232" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/innowine/</t>
+        </is>
+      </c>
+      <c r="U232" s="2" t="inlineStr"/>
+      <c r="V232" s="2" t="inlineStr"/>
+      <c r="W232" s="2" t="inlineStr">
+        <is>
+          <t>Csaba Zoltán Várkonyi</t>
+        </is>
+      </c>
+      <c r="X232" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y232" s="2" t="inlineStr"/>
+      <c r="Z232" s="2" t="inlineStr"/>
+      <c r="AA232" s="2" t="inlineStr"/>
+    </row>
+    <row r="233">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>KISBOSA-KER Korlátolt Felelosségu Társaság</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>KISBOSA-KER Kft.</t>
+        </is>
+      </c>
+      <c r="C233" s="2" t="inlineStr">
+        <is>
+          <t>167823</t>
+        </is>
+      </c>
+      <c r="D233" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E233" s="2" t="inlineStr">
+        <is>
+          <t>Kóka</t>
+        </is>
+      </c>
+      <c r="F233" s="2" t="inlineStr">
+        <is>
+          <t>Pest Megye</t>
+        </is>
+      </c>
+      <c r="G233" s="2" t="inlineStr">
+        <is>
+          <t>Felsovásár tér 24/A</t>
+        </is>
+      </c>
+      <c r="H233" s="2" t="inlineStr">
+        <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>https://kissbkerkft.hu</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr"/>
+      <c r="K233" s="2" t="inlineStr"/>
+      <c r="L233" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M233" s="2" t="inlineStr">
+        <is>
+          <t>194655</t>
+        </is>
+      </c>
+      <c r="N233" s="2" t="inlineStr">
+        <is>
+          <t>info@kissbkerkft.hu</t>
+        </is>
+      </c>
+      <c r="O233" s="2" t="inlineStr"/>
+      <c r="P233" s="2" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="Q233" s="2" t="inlineStr">
+        <is>
+          <t>26246958213</t>
+        </is>
+      </c>
+      <c r="R233" s="2" t="inlineStr"/>
+      <c r="S233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/kissbkerkft</t>
+        </is>
+      </c>
+      <c r="T233" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/kissbkerkft</t>
+        </is>
+      </c>
+      <c r="U233" s="2" t="inlineStr"/>
+      <c r="V233" s="2" t="inlineStr"/>
+      <c r="W233" s="2" t="inlineStr"/>
+      <c r="X233" s="2" t="inlineStr"/>
+      <c r="Y233" s="2" t="inlineStr"/>
+      <c r="Z233" s="2" t="inlineStr"/>
+      <c r="AA233" s="2" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" s="2" t="inlineStr">
+        <is>
+          <t>Match the Wine Korlátolt Felelosségu Társaság</t>
+        </is>
+      </c>
+      <c r="B234" s="2" t="inlineStr">
+        <is>
+          <t>Match the Wine Kft.</t>
+        </is>
+      </c>
+      <c r="C234" s="2" t="inlineStr">
+        <is>
+          <t>167821</t>
+        </is>
+      </c>
+      <c r="D234" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E234" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F234" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="G234" s="2" t="inlineStr">
+        <is>
+          <t>Meder utca 2-4. B. lház. 9. em. 7. ajtó</t>
+        </is>
+      </c>
+      <c r="H234" s="2" t="inlineStr">
+        <is>
+          <t>1138</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>https://matchthewine.com</t>
+        </is>
+      </c>
+      <c r="J234" s="2" t="inlineStr"/>
+      <c r="K234" s="2" t="inlineStr"/>
+      <c r="L234" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M234" s="2" t="inlineStr">
+        <is>
+          <t>49000</t>
+        </is>
+      </c>
+      <c r="N234" s="2" t="inlineStr">
+        <is>
+          <t>hello@matchthewine.com</t>
+        </is>
+      </c>
+      <c r="O234" s="2" t="inlineStr"/>
+      <c r="P234" s="2" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="Q234" s="2" t="inlineStr">
+        <is>
+          <t>32724017241</t>
+        </is>
+      </c>
+      <c r="R234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/match-the-wine/</t>
+        </is>
+      </c>
+      <c r="S234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/profile.php?id=61571933421128</t>
+        </is>
+      </c>
+      <c r="T234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/matchthewine/</t>
+        </is>
+      </c>
+      <c r="U234" s="2" t="inlineStr"/>
+      <c r="V234" s="2" t="inlineStr"/>
+      <c r="W234" s="2" t="inlineStr">
+        <is>
+          <t>Dániel Terjéki</t>
+        </is>
+      </c>
+      <c r="X234" s="2" t="inlineStr">
+        <is>
+          <t>Co-Founder</t>
+        </is>
+      </c>
+      <c r="Y234" s="2" t="inlineStr"/>
+      <c r="Z234" s="2" t="inlineStr"/>
+      <c r="AA234" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/daniel-terjeki-47742051/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hungary.xlsx
+++ b/BWI/bestwine_output/bestwine_Hungary.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA234"/>
+  <dimension ref="A1:AA235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -25282,6 +25282,103 @@
         </is>
       </c>
     </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>Transylwine Kft.</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>Transylwine Kft.</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>108192</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr"/>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>Kmety György u. 15. 3rd floor, 1st floor</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>1063</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>https://borkell.hu, https://transylwine.hu</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr"/>
+      <c r="K235" s="2" t="inlineStr"/>
+      <c r="L235" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M235" s="2" t="inlineStr"/>
+      <c r="N235" s="2" t="inlineStr">
+        <is>
+          <t>info@borkell.hu</t>
+        </is>
+      </c>
+      <c r="O235" s="2" t="inlineStr"/>
+      <c r="P235" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q235" s="2" t="inlineStr">
+        <is>
+          <t>11747154242</t>
+        </is>
+      </c>
+      <c r="R235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/borkell-hu/</t>
+        </is>
+      </c>
+      <c r="S235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/borkell.hu/</t>
+        </is>
+      </c>
+      <c r="T235" s="2" t="inlineStr"/>
+      <c r="U235" s="2" t="inlineStr"/>
+      <c r="V235" s="2" t="inlineStr"/>
+      <c r="W235" s="2" t="inlineStr">
+        <is>
+          <t>Tóth Attila</t>
+        </is>
+      </c>
+      <c r="X235" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director &amp; Owner</t>
+        </is>
+      </c>
+      <c r="Y235" s="2" t="inlineStr"/>
+      <c r="Z235" s="2" t="inlineStr"/>
+      <c r="AA235" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/attila-toth-oly-b837496/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hungary.xlsx
+++ b/BWI/bestwine_output/bestwine_Hungary.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA235"/>
+  <dimension ref="A1:AA240"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -25379,6 +25379,491 @@
         </is>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>Mátrai Borok Háza</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>Mátrai Borok Háza</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>28538</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>Gyöngyös</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>North Hungary</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>16 Mátrai út</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>https://matraiborokhaza.hu</t>
+        </is>
+      </c>
+      <c r="J236" s="2" t="inlineStr"/>
+      <c r="K236" s="2" t="inlineStr"/>
+      <c r="L236" s="2" t="inlineStr"/>
+      <c r="M236" s="2" t="inlineStr"/>
+      <c r="N236" s="2" t="inlineStr">
+        <is>
+          <t>info@matraiborokhaza.hu</t>
+        </is>
+      </c>
+      <c r="O236" s="2" t="inlineStr"/>
+      <c r="P236" s="2" t="inlineStr"/>
+      <c r="Q236" s="2" t="inlineStr"/>
+      <c r="R236" s="2" t="inlineStr"/>
+      <c r="S236" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/matraiborokhaza/</t>
+        </is>
+      </c>
+      <c r="T236" s="2" t="inlineStr"/>
+      <c r="U236" s="2" t="inlineStr"/>
+      <c r="V236" s="2" t="inlineStr"/>
+      <c r="W236" s="2" t="inlineStr"/>
+      <c r="X236" s="2" t="inlineStr"/>
+      <c r="Y236" s="2" t="inlineStr"/>
+      <c r="Z236" s="2" t="inlineStr"/>
+      <c r="AA236" s="2" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>7867</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>2 Szőlőkert köz</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="inlineStr"/>
+      <c r="K237" s="2" t="inlineStr"/>
+      <c r="L237" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M237" s="2" t="inlineStr"/>
+      <c r="N237" s="2" t="inlineStr">
+        <is>
+          <t>webshop@borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="O237" s="2" t="inlineStr"/>
+      <c r="P237" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q237" s="2" t="inlineStr">
+        <is>
+          <t>23316564242</t>
+        </is>
+      </c>
+      <c r="R237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/veritas-borkeresked%C3%A9s-www-borkereskedes-hu/</t>
+        </is>
+      </c>
+      <c r="S237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/veritasborkereskedes/</t>
+        </is>
+      </c>
+      <c r="T237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veritas_borkereskedes/</t>
+        </is>
+      </c>
+      <c r="U237" s="2" t="inlineStr"/>
+      <c r="V237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCeGWTJE4hTW-0GbB1HK3yMw</t>
+        </is>
+      </c>
+      <c r="W237" s="2" t="inlineStr">
+        <is>
+          <t>Dezső Diószegi</t>
+        </is>
+      </c>
+      <c r="X237" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y237" s="2" t="inlineStr"/>
+      <c r="Z237" s="2" t="inlineStr"/>
+      <c r="AA237" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dezs%C5%91-di%C3%B3szegi-81023b3b/?originalSubdomain=hu</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>7867</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>2 Szőlőkert köz</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="inlineStr"/>
+      <c r="K238" s="2" t="inlineStr"/>
+      <c r="L238" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M238" s="2" t="inlineStr"/>
+      <c r="N238" s="2" t="inlineStr">
+        <is>
+          <t>webshop@borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="O238" s="2" t="inlineStr"/>
+      <c r="P238" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q238" s="2" t="inlineStr">
+        <is>
+          <t>23316564242</t>
+        </is>
+      </c>
+      <c r="R238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/veritas-borkeresked%C3%A9s-www-borkereskedes-hu/</t>
+        </is>
+      </c>
+      <c r="S238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/veritasborkereskedes/</t>
+        </is>
+      </c>
+      <c r="T238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veritas_borkereskedes/</t>
+        </is>
+      </c>
+      <c r="U238" s="2" t="inlineStr"/>
+      <c r="V238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCeGWTJE4hTW-0GbB1HK3yMw</t>
+        </is>
+      </c>
+      <c r="W238" s="2" t="inlineStr">
+        <is>
+          <t>Tibor Kovács</t>
+        </is>
+      </c>
+      <c r="X238" s="2" t="inlineStr">
+        <is>
+          <t>International Wine Advisor</t>
+        </is>
+      </c>
+      <c r="Y238" s="2" t="inlineStr"/>
+      <c r="Z238" s="2" t="inlineStr"/>
+      <c r="AA238" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tibor-kov%C3%A1cs-a78026164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="2" t="inlineStr">
+        <is>
+          <t>Bormánia Kereskedelmi Kft.</t>
+        </is>
+      </c>
+      <c r="B239" s="2" t="inlineStr">
+        <is>
+          <t>Bormánia Kereskedelmi Kft.</t>
+        </is>
+      </c>
+      <c r="C239" s="2" t="inlineStr">
+        <is>
+          <t>24149</t>
+        </is>
+      </c>
+      <c r="D239" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E239" s="2" t="inlineStr">
+        <is>
+          <t>Dunakeszi</t>
+        </is>
+      </c>
+      <c r="F239" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G239" s="2" t="inlineStr">
+        <is>
+          <t>89 Fő út</t>
+        </is>
+      </c>
+      <c r="H239" s="2" t="inlineStr">
+        <is>
+          <t>2120</t>
+        </is>
+      </c>
+      <c r="I239" s="2" t="inlineStr">
+        <is>
+          <t>https://bormania.hu</t>
+        </is>
+      </c>
+      <c r="J239" s="2" t="inlineStr"/>
+      <c r="K239" s="2" t="inlineStr"/>
+      <c r="L239" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M239" s="2" t="inlineStr"/>
+      <c r="N239" s="2" t="inlineStr">
+        <is>
+          <t>info@bormania.hu</t>
+        </is>
+      </c>
+      <c r="O239" s="2" t="inlineStr">
+        <is>
+          <t>+36 27 739 223</t>
+        </is>
+      </c>
+      <c r="P239" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q239" s="2" t="inlineStr">
+        <is>
+          <t>11981330213</t>
+        </is>
+      </c>
+      <c r="R239" s="2" t="inlineStr"/>
+      <c r="S239" s="2" t="inlineStr"/>
+      <c r="T239" s="2" t="inlineStr"/>
+      <c r="U239" s="2" t="inlineStr"/>
+      <c r="V239" s="2" t="inlineStr"/>
+      <c r="W239" s="2" t="inlineStr">
+        <is>
+          <t>Kiss Zsolt</t>
+        </is>
+      </c>
+      <c r="X239" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y239" s="2" t="inlineStr"/>
+      <c r="Z239" s="2" t="inlineStr"/>
+      <c r="AA239" s="2" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" s="2" t="inlineStr">
+        <is>
+          <t>Selection.hu Kft.</t>
+        </is>
+      </c>
+      <c r="B240" s="2" t="inlineStr">
+        <is>
+          <t>Selection.hu Kft.</t>
+        </is>
+      </c>
+      <c r="C240" s="2" t="inlineStr">
+        <is>
+          <t>7857</t>
+        </is>
+      </c>
+      <c r="D240" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E240" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F240" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G240" s="2" t="inlineStr">
+        <is>
+          <t>91 Lajos utca</t>
+        </is>
+      </c>
+      <c r="H240" s="2" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>https://selection.hu</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr"/>
+      <c r="K240" s="2" t="inlineStr"/>
+      <c r="L240" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M240" s="2" t="inlineStr"/>
+      <c r="N240" s="2" t="inlineStr">
+        <is>
+          <t>info@selection.hu</t>
+        </is>
+      </c>
+      <c r="O240" s="2" t="inlineStr">
+        <is>
+          <t>+36 1 439 1902</t>
+        </is>
+      </c>
+      <c r="P240" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q240" s="2" t="inlineStr">
+        <is>
+          <t>27104750241</t>
+        </is>
+      </c>
+      <c r="R240" s="2" t="inlineStr"/>
+      <c r="S240" s="2" t="inlineStr"/>
+      <c r="T240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/selection_hu/</t>
+        </is>
+      </c>
+      <c r="U240" s="2" t="inlineStr"/>
+      <c r="V240" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@selectionhu/</t>
+        </is>
+      </c>
+      <c r="W240" s="2" t="inlineStr">
+        <is>
+          <t>Tamás Lakatos</t>
+        </is>
+      </c>
+      <c r="X240" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y240" s="2" t="inlineStr"/>
+      <c r="Z240" s="2" t="inlineStr"/>
+      <c r="AA240" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hungary.xlsx
+++ b/BWI/bestwine_output/bestwine_Hungary.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA240"/>
+  <dimension ref="A1:AA247"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -25864,6 +25864,689 @@
       <c r="Z240" s="2" t="inlineStr"/>
       <c r="AA240" s="2" t="inlineStr"/>
     </row>
+    <row r="241">
+      <c r="A241" s="2" t="inlineStr">
+        <is>
+          <t>Wine Mission Kft</t>
+        </is>
+      </c>
+      <c r="B241" s="2" t="inlineStr">
+        <is>
+          <t>Wine Mission Kft</t>
+        </is>
+      </c>
+      <c r="C241" s="2" t="inlineStr">
+        <is>
+          <t>35601</t>
+        </is>
+      </c>
+      <c r="D241" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E241" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F241" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G241" s="2" t="inlineStr">
+        <is>
+          <t>37 Nándorfejérvári út</t>
+        </is>
+      </c>
+      <c r="H241" s="2" t="inlineStr">
+        <is>
+          <t>1116</t>
+        </is>
+      </c>
+      <c r="I241" s="2" t="inlineStr">
+        <is>
+          <t>https://winemission.hu</t>
+        </is>
+      </c>
+      <c r="J241" s="2" t="inlineStr"/>
+      <c r="K241" s="2" t="inlineStr"/>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M241" s="2" t="inlineStr"/>
+      <c r="N241" s="2" t="inlineStr">
+        <is>
+          <t>info@winemission.hu</t>
+        </is>
+      </c>
+      <c r="O241" s="2" t="inlineStr"/>
+      <c r="P241" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q241" s="2" t="inlineStr">
+        <is>
+          <t>24270661213</t>
+        </is>
+      </c>
+      <c r="R241" s="2" t="inlineStr"/>
+      <c r="S241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winemission/</t>
+        </is>
+      </c>
+      <c r="T241" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wine_mission_hungary</t>
+        </is>
+      </c>
+      <c r="U241" s="2" t="inlineStr"/>
+      <c r="V241" s="2" t="inlineStr"/>
+      <c r="W241" s="2" t="inlineStr">
+        <is>
+          <t>Viktor Farkas</t>
+        </is>
+      </c>
+      <c r="X241" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y241" s="2" t="inlineStr"/>
+      <c r="Z241" s="2" t="inlineStr"/>
+      <c r="AA241" s="2" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" s="2" t="inlineStr">
+        <is>
+          <t>Bormental Doktor Korlátolt Felelosségu Társaság</t>
+        </is>
+      </c>
+      <c r="B242" s="2" t="inlineStr">
+        <is>
+          <t>Bormental Doktor Korlátolt Felelosségu Társaság</t>
+        </is>
+      </c>
+      <c r="C242" s="2" t="inlineStr">
+        <is>
+          <t>29986</t>
+        </is>
+      </c>
+      <c r="D242" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E242" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F242" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G242" s="2" t="inlineStr">
+        <is>
+          <t>5-7 Derék utca</t>
+        </is>
+      </c>
+      <c r="H242" s="2" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="I242" s="2" t="inlineStr">
+        <is>
+          <t>https://bolgarborok.hu</t>
+        </is>
+      </c>
+      <c r="J242" s="2" t="inlineStr"/>
+      <c r="K242" s="2" t="inlineStr"/>
+      <c r="L242" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M242" s="2" t="inlineStr"/>
+      <c r="N242" s="2" t="inlineStr">
+        <is>
+          <t>ambassador@bolgarborok.hu</t>
+        </is>
+      </c>
+      <c r="O242" s="2" t="inlineStr"/>
+      <c r="P242" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q242" s="2" t="inlineStr">
+        <is>
+          <t>22614546241</t>
+        </is>
+      </c>
+      <c r="R242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bulgarian-wine-embassy/</t>
+        </is>
+      </c>
+      <c r="S242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bolgarborok/</t>
+        </is>
+      </c>
+      <c r="T242" s="2" t="inlineStr"/>
+      <c r="U242" s="2" t="inlineStr"/>
+      <c r="V242" s="2" t="inlineStr"/>
+      <c r="W242" s="2" t="inlineStr">
+        <is>
+          <t>Rossen Tkatchenko</t>
+        </is>
+      </c>
+      <c r="X242" s="2" t="inlineStr">
+        <is>
+          <t>Ambassador</t>
+        </is>
+      </c>
+      <c r="Y242" s="2" t="inlineStr"/>
+      <c r="Z242" s="2" t="inlineStr"/>
+      <c r="AA242" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rossent/</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="2" t="inlineStr">
+        <is>
+          <t>Mátrai Borok Háza</t>
+        </is>
+      </c>
+      <c r="B243" s="2" t="inlineStr">
+        <is>
+          <t>Mátrai Borok Háza</t>
+        </is>
+      </c>
+      <c r="C243" s="2" t="inlineStr">
+        <is>
+          <t>28538</t>
+        </is>
+      </c>
+      <c r="D243" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E243" s="2" t="inlineStr">
+        <is>
+          <t>Gyöngyös</t>
+        </is>
+      </c>
+      <c r="F243" s="2" t="inlineStr">
+        <is>
+          <t>North Hungary</t>
+        </is>
+      </c>
+      <c r="G243" s="2" t="inlineStr">
+        <is>
+          <t>16 Mátrai út</t>
+        </is>
+      </c>
+      <c r="H243" s="2" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="I243" s="2" t="inlineStr">
+        <is>
+          <t>https://matraiborokhaza.hu</t>
+        </is>
+      </c>
+      <c r="J243" s="2" t="inlineStr"/>
+      <c r="K243" s="2" t="inlineStr"/>
+      <c r="L243" s="2" t="inlineStr"/>
+      <c r="M243" s="2" t="inlineStr"/>
+      <c r="N243" s="2" t="inlineStr">
+        <is>
+          <t>info@matraiborokhaza.hu</t>
+        </is>
+      </c>
+      <c r="O243" s="2" t="inlineStr"/>
+      <c r="P243" s="2" t="inlineStr"/>
+      <c r="Q243" s="2" t="inlineStr"/>
+      <c r="R243" s="2" t="inlineStr"/>
+      <c r="S243" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/matraiborokhaza/</t>
+        </is>
+      </c>
+      <c r="T243" s="2" t="inlineStr"/>
+      <c r="U243" s="2" t="inlineStr"/>
+      <c r="V243" s="2" t="inlineStr"/>
+      <c r="W243" s="2" t="inlineStr"/>
+      <c r="X243" s="2" t="inlineStr"/>
+      <c r="Y243" s="2" t="inlineStr"/>
+      <c r="Z243" s="2" t="inlineStr"/>
+      <c r="AA243" s="2" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="C244" s="2" t="inlineStr">
+        <is>
+          <t>7867</t>
+        </is>
+      </c>
+      <c r="D244" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E244" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F244" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>2 Szőlőkert köz</t>
+        </is>
+      </c>
+      <c r="H244" s="2" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="J244" s="2" t="inlineStr"/>
+      <c r="K244" s="2" t="inlineStr"/>
+      <c r="L244" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M244" s="2" t="inlineStr"/>
+      <c r="N244" s="2" t="inlineStr">
+        <is>
+          <t>webshop@borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="O244" s="2" t="inlineStr"/>
+      <c r="P244" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q244" s="2" t="inlineStr">
+        <is>
+          <t>23316564242</t>
+        </is>
+      </c>
+      <c r="R244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/veritas-borkeresked%C3%A9s-www-borkereskedes-hu/</t>
+        </is>
+      </c>
+      <c r="S244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/veritasborkereskedes/</t>
+        </is>
+      </c>
+      <c r="T244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veritas_borkereskedes/</t>
+        </is>
+      </c>
+      <c r="U244" s="2" t="inlineStr"/>
+      <c r="V244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCeGWTJE4hTW-0GbB1HK3yMw</t>
+        </is>
+      </c>
+      <c r="W244" s="2" t="inlineStr">
+        <is>
+          <t>Dezső Diószegi</t>
+        </is>
+      </c>
+      <c r="X244" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y244" s="2" t="inlineStr"/>
+      <c r="Z244" s="2" t="inlineStr"/>
+      <c r="AA244" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dezs%C5%91-di%C3%B3szegi-81023b3b/?originalSubdomain=hu</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="B245" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="C245" s="2" t="inlineStr">
+        <is>
+          <t>7867</t>
+        </is>
+      </c>
+      <c r="D245" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E245" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F245" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G245" s="2" t="inlineStr">
+        <is>
+          <t>2 Szőlőkert köz</t>
+        </is>
+      </c>
+      <c r="H245" s="2" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="I245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="J245" s="2" t="inlineStr"/>
+      <c r="K245" s="2" t="inlineStr"/>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M245" s="2" t="inlineStr"/>
+      <c r="N245" s="2" t="inlineStr">
+        <is>
+          <t>webshop@borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="O245" s="2" t="inlineStr"/>
+      <c r="P245" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q245" s="2" t="inlineStr">
+        <is>
+          <t>23316564242</t>
+        </is>
+      </c>
+      <c r="R245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/veritas-borkeresked%C3%A9s-www-borkereskedes-hu/</t>
+        </is>
+      </c>
+      <c r="S245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/veritasborkereskedes/</t>
+        </is>
+      </c>
+      <c r="T245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veritas_borkereskedes/</t>
+        </is>
+      </c>
+      <c r="U245" s="2" t="inlineStr"/>
+      <c r="V245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCeGWTJE4hTW-0GbB1HK3yMw</t>
+        </is>
+      </c>
+      <c r="W245" s="2" t="inlineStr">
+        <is>
+          <t>Tibor Kovács</t>
+        </is>
+      </c>
+      <c r="X245" s="2" t="inlineStr">
+        <is>
+          <t>International Wine Advisor</t>
+        </is>
+      </c>
+      <c r="Y245" s="2" t="inlineStr"/>
+      <c r="Z245" s="2" t="inlineStr"/>
+      <c r="AA245" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tibor-kov%C3%A1cs-a78026164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
+        <is>
+          <t>Bormánia Kereskedelmi Kft.</t>
+        </is>
+      </c>
+      <c r="B246" s="2" t="inlineStr">
+        <is>
+          <t>Bormánia Kereskedelmi Kft.</t>
+        </is>
+      </c>
+      <c r="C246" s="2" t="inlineStr">
+        <is>
+          <t>24149</t>
+        </is>
+      </c>
+      <c r="D246" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E246" s="2" t="inlineStr">
+        <is>
+          <t>Dunakeszi</t>
+        </is>
+      </c>
+      <c r="F246" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G246" s="2" t="inlineStr">
+        <is>
+          <t>89 Fő út</t>
+        </is>
+      </c>
+      <c r="H246" s="2" t="inlineStr">
+        <is>
+          <t>2120</t>
+        </is>
+      </c>
+      <c r="I246" s="2" t="inlineStr">
+        <is>
+          <t>https://bormania.hu</t>
+        </is>
+      </c>
+      <c r="J246" s="2" t="inlineStr"/>
+      <c r="K246" s="2" t="inlineStr"/>
+      <c r="L246" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M246" s="2" t="inlineStr"/>
+      <c r="N246" s="2" t="inlineStr">
+        <is>
+          <t>info@bormania.hu</t>
+        </is>
+      </c>
+      <c r="O246" s="2" t="inlineStr">
+        <is>
+          <t>+36 27 739 223</t>
+        </is>
+      </c>
+      <c r="P246" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q246" s="2" t="inlineStr">
+        <is>
+          <t>11981330213</t>
+        </is>
+      </c>
+      <c r="R246" s="2" t="inlineStr"/>
+      <c r="S246" s="2" t="inlineStr"/>
+      <c r="T246" s="2" t="inlineStr"/>
+      <c r="U246" s="2" t="inlineStr"/>
+      <c r="V246" s="2" t="inlineStr"/>
+      <c r="W246" s="2" t="inlineStr">
+        <is>
+          <t>Kiss Zsolt</t>
+        </is>
+      </c>
+      <c r="X246" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y246" s="2" t="inlineStr"/>
+      <c r="Z246" s="2" t="inlineStr"/>
+      <c r="AA246" s="2" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>Selection.hu Kft.</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>Selection.hu Kft.</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>7857</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>91 Lajos utca</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>https://selection.hu</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr"/>
+      <c r="K247" s="2" t="inlineStr"/>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M247" s="2" t="inlineStr"/>
+      <c r="N247" s="2" t="inlineStr">
+        <is>
+          <t>info@selection.hu</t>
+        </is>
+      </c>
+      <c r="O247" s="2" t="inlineStr">
+        <is>
+          <t>+36 1 439 1902</t>
+        </is>
+      </c>
+      <c r="P247" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q247" s="2" t="inlineStr">
+        <is>
+          <t>27104750241</t>
+        </is>
+      </c>
+      <c r="R247" s="2" t="inlineStr"/>
+      <c r="S247" s="2" t="inlineStr"/>
+      <c r="T247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/selection_hu/</t>
+        </is>
+      </c>
+      <c r="U247" s="2" t="inlineStr"/>
+      <c r="V247" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@selectionhu/</t>
+        </is>
+      </c>
+      <c r="W247" s="2" t="inlineStr">
+        <is>
+          <t>Tamás Lakatos</t>
+        </is>
+      </c>
+      <c r="X247" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y247" s="2" t="inlineStr"/>
+      <c r="Z247" s="2" t="inlineStr"/>
+      <c r="AA247" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hungary.xlsx
+++ b/BWI/bestwine_output/bestwine_Hungary.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA247"/>
+  <dimension ref="A1:AA254"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -26547,6 +26547,689 @@
       <c r="Z247" s="2" t="inlineStr"/>
       <c r="AA247" s="2" t="inlineStr"/>
     </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>Wine Mission Kft</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>Wine Mission Kft</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>35601</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>37 Nándorfejérvári út</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>1116</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>https://winemission.hu</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr"/>
+      <c r="K248" s="2" t="inlineStr"/>
+      <c r="L248" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M248" s="2" t="inlineStr"/>
+      <c r="N248" s="2" t="inlineStr">
+        <is>
+          <t>info@winemission.hu</t>
+        </is>
+      </c>
+      <c r="O248" s="2" t="inlineStr"/>
+      <c r="P248" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q248" s="2" t="inlineStr">
+        <is>
+          <t>24270661213</t>
+        </is>
+      </c>
+      <c r="R248" s="2" t="inlineStr"/>
+      <c r="S248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winemission/</t>
+        </is>
+      </c>
+      <c r="T248" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wine_mission_hungary</t>
+        </is>
+      </c>
+      <c r="U248" s="2" t="inlineStr"/>
+      <c r="V248" s="2" t="inlineStr"/>
+      <c r="W248" s="2" t="inlineStr">
+        <is>
+          <t>Viktor Farkas</t>
+        </is>
+      </c>
+      <c r="X248" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y248" s="2" t="inlineStr"/>
+      <c r="Z248" s="2" t="inlineStr"/>
+      <c r="AA248" s="2" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>Bormental Doktor Korlátolt Felelosségu Társaság</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>Bormental Doktor Korlátolt Felelosségu Társaság</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>29986</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>5-7 Derék utca</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>https://bolgarborok.hu</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr"/>
+      <c r="K249" s="2" t="inlineStr"/>
+      <c r="L249" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="inlineStr"/>
+      <c r="N249" s="2" t="inlineStr">
+        <is>
+          <t>ambassador@bolgarborok.hu</t>
+        </is>
+      </c>
+      <c r="O249" s="2" t="inlineStr"/>
+      <c r="P249" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q249" s="2" t="inlineStr">
+        <is>
+          <t>22614546241</t>
+        </is>
+      </c>
+      <c r="R249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bulgarian-wine-embassy/</t>
+        </is>
+      </c>
+      <c r="S249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bolgarborok/</t>
+        </is>
+      </c>
+      <c r="T249" s="2" t="inlineStr"/>
+      <c r="U249" s="2" t="inlineStr"/>
+      <c r="V249" s="2" t="inlineStr"/>
+      <c r="W249" s="2" t="inlineStr">
+        <is>
+          <t>Rossen Tkatchenko</t>
+        </is>
+      </c>
+      <c r="X249" s="2" t="inlineStr">
+        <is>
+          <t>Ambassador</t>
+        </is>
+      </c>
+      <c r="Y249" s="2" t="inlineStr"/>
+      <c r="Z249" s="2" t="inlineStr"/>
+      <c r="AA249" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rossent/</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>Mátrai Borok Háza</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Mátrai Borok Háza</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>28538</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>Gyöngyös</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>North Hungary</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>16 Mátrai út</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>https://matraiborokhaza.hu</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr"/>
+      <c r="K250" s="2" t="inlineStr"/>
+      <c r="L250" s="2" t="inlineStr"/>
+      <c r="M250" s="2" t="inlineStr"/>
+      <c r="N250" s="2" t="inlineStr">
+        <is>
+          <t>info@matraiborokhaza.hu</t>
+        </is>
+      </c>
+      <c r="O250" s="2" t="inlineStr"/>
+      <c r="P250" s="2" t="inlineStr"/>
+      <c r="Q250" s="2" t="inlineStr"/>
+      <c r="R250" s="2" t="inlineStr"/>
+      <c r="S250" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/matraiborokhaza/</t>
+        </is>
+      </c>
+      <c r="T250" s="2" t="inlineStr"/>
+      <c r="U250" s="2" t="inlineStr"/>
+      <c r="V250" s="2" t="inlineStr"/>
+      <c r="W250" s="2" t="inlineStr"/>
+      <c r="X250" s="2" t="inlineStr"/>
+      <c r="Y250" s="2" t="inlineStr"/>
+      <c r="Z250" s="2" t="inlineStr"/>
+      <c r="AA250" s="2" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>7867</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>2 Szőlőkert köz</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="J251" s="2" t="inlineStr"/>
+      <c r="K251" s="2" t="inlineStr"/>
+      <c r="L251" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M251" s="2" t="inlineStr"/>
+      <c r="N251" s="2" t="inlineStr">
+        <is>
+          <t>webshop@borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="O251" s="2" t="inlineStr"/>
+      <c r="P251" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q251" s="2" t="inlineStr">
+        <is>
+          <t>23316564242</t>
+        </is>
+      </c>
+      <c r="R251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/veritas-borkeresked%C3%A9s-www-borkereskedes-hu/</t>
+        </is>
+      </c>
+      <c r="S251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/veritasborkereskedes/</t>
+        </is>
+      </c>
+      <c r="T251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veritas_borkereskedes/</t>
+        </is>
+      </c>
+      <c r="U251" s="2" t="inlineStr"/>
+      <c r="V251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCeGWTJE4hTW-0GbB1HK3yMw</t>
+        </is>
+      </c>
+      <c r="W251" s="2" t="inlineStr">
+        <is>
+          <t>Dezső Diószegi</t>
+        </is>
+      </c>
+      <c r="X251" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y251" s="2" t="inlineStr"/>
+      <c r="Z251" s="2" t="inlineStr"/>
+      <c r="AA251" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dezs%C5%91-di%C3%B3szegi-81023b3b/?originalSubdomain=hu</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>7867</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>2 Szőlőkert köz</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr"/>
+      <c r="K252" s="2" t="inlineStr"/>
+      <c r="L252" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="inlineStr"/>
+      <c r="N252" s="2" t="inlineStr">
+        <is>
+          <t>webshop@borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="O252" s="2" t="inlineStr"/>
+      <c r="P252" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q252" s="2" t="inlineStr">
+        <is>
+          <t>23316564242</t>
+        </is>
+      </c>
+      <c r="R252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/veritas-borkeresked%C3%A9s-www-borkereskedes-hu/</t>
+        </is>
+      </c>
+      <c r="S252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/veritasborkereskedes/</t>
+        </is>
+      </c>
+      <c r="T252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veritas_borkereskedes/</t>
+        </is>
+      </c>
+      <c r="U252" s="2" t="inlineStr"/>
+      <c r="V252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCeGWTJE4hTW-0GbB1HK3yMw</t>
+        </is>
+      </c>
+      <c r="W252" s="2" t="inlineStr">
+        <is>
+          <t>Tibor Kovács</t>
+        </is>
+      </c>
+      <c r="X252" s="2" t="inlineStr">
+        <is>
+          <t>International Wine Advisor</t>
+        </is>
+      </c>
+      <c r="Y252" s="2" t="inlineStr"/>
+      <c r="Z252" s="2" t="inlineStr"/>
+      <c r="AA252" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tibor-kov%C3%A1cs-a78026164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>Bormánia Kereskedelmi Kft.</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>Bormánia Kereskedelmi Kft.</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>24149</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>Dunakeszi</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>89 Fő út</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>2120</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>https://bormania.hu</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr"/>
+      <c r="K253" s="2" t="inlineStr"/>
+      <c r="L253" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M253" s="2" t="inlineStr"/>
+      <c r="N253" s="2" t="inlineStr">
+        <is>
+          <t>info@bormania.hu</t>
+        </is>
+      </c>
+      <c r="O253" s="2" t="inlineStr">
+        <is>
+          <t>+36 27 739 223</t>
+        </is>
+      </c>
+      <c r="P253" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q253" s="2" t="inlineStr">
+        <is>
+          <t>11981330213</t>
+        </is>
+      </c>
+      <c r="R253" s="2" t="inlineStr"/>
+      <c r="S253" s="2" t="inlineStr"/>
+      <c r="T253" s="2" t="inlineStr"/>
+      <c r="U253" s="2" t="inlineStr"/>
+      <c r="V253" s="2" t="inlineStr"/>
+      <c r="W253" s="2" t="inlineStr">
+        <is>
+          <t>Kiss Zsolt</t>
+        </is>
+      </c>
+      <c r="X253" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y253" s="2" t="inlineStr"/>
+      <c r="Z253" s="2" t="inlineStr"/>
+      <c r="AA253" s="2" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>Selection.hu Kft.</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>Selection.hu Kft.</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>7857</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>91 Lajos utca</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>https://selection.hu</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr"/>
+      <c r="K254" s="2" t="inlineStr"/>
+      <c r="L254" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M254" s="2" t="inlineStr"/>
+      <c r="N254" s="2" t="inlineStr">
+        <is>
+          <t>info@selection.hu</t>
+        </is>
+      </c>
+      <c r="O254" s="2" t="inlineStr">
+        <is>
+          <t>+36 1 439 1902</t>
+        </is>
+      </c>
+      <c r="P254" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q254" s="2" t="inlineStr">
+        <is>
+          <t>27104750241</t>
+        </is>
+      </c>
+      <c r="R254" s="2" t="inlineStr"/>
+      <c r="S254" s="2" t="inlineStr"/>
+      <c r="T254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/selection_hu/</t>
+        </is>
+      </c>
+      <c r="U254" s="2" t="inlineStr"/>
+      <c r="V254" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@selectionhu/</t>
+        </is>
+      </c>
+      <c r="W254" s="2" t="inlineStr">
+        <is>
+          <t>Tamás Lakatos</t>
+        </is>
+      </c>
+      <c r="X254" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y254" s="2" t="inlineStr"/>
+      <c r="Z254" s="2" t="inlineStr"/>
+      <c r="AA254" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hungary.xlsx
+++ b/BWI/bestwine_output/bestwine_Hungary.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA254"/>
+  <dimension ref="A1:AA261"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -27230,6 +27230,689 @@
       <c r="Z254" s="2" t="inlineStr"/>
       <c r="AA254" s="2" t="inlineStr"/>
     </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Wine Mission Kft</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>Wine Mission Kft</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>35601</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>37 Nándorfejérvári út</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>1116</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>https://winemission.hu</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr"/>
+      <c r="K255" s="2" t="inlineStr"/>
+      <c r="L255" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M255" s="2" t="inlineStr"/>
+      <c r="N255" s="2" t="inlineStr">
+        <is>
+          <t>info@winemission.hu</t>
+        </is>
+      </c>
+      <c r="O255" s="2" t="inlineStr"/>
+      <c r="P255" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q255" s="2" t="inlineStr">
+        <is>
+          <t>24270661213</t>
+        </is>
+      </c>
+      <c r="R255" s="2" t="inlineStr"/>
+      <c r="S255" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winemission/</t>
+        </is>
+      </c>
+      <c r="T255" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wine_mission_hungary</t>
+        </is>
+      </c>
+      <c r="U255" s="2" t="inlineStr"/>
+      <c r="V255" s="2" t="inlineStr"/>
+      <c r="W255" s="2" t="inlineStr">
+        <is>
+          <t>Viktor Farkas</t>
+        </is>
+      </c>
+      <c r="X255" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y255" s="2" t="inlineStr"/>
+      <c r="Z255" s="2" t="inlineStr"/>
+      <c r="AA255" s="2" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>Bormental Doktor Korlátolt Felelosségu Társaság</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>Bormental Doktor Korlátolt Felelosségu Társaság</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>29986</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>5-7 Derék utca</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>https://bolgarborok.hu</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr"/>
+      <c r="K256" s="2" t="inlineStr"/>
+      <c r="L256" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M256" s="2" t="inlineStr"/>
+      <c r="N256" s="2" t="inlineStr">
+        <is>
+          <t>ambassador@bolgarborok.hu</t>
+        </is>
+      </c>
+      <c r="O256" s="2" t="inlineStr"/>
+      <c r="P256" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q256" s="2" t="inlineStr">
+        <is>
+          <t>22614546241</t>
+        </is>
+      </c>
+      <c r="R256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bulgarian-wine-embassy/</t>
+        </is>
+      </c>
+      <c r="S256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bolgarborok/</t>
+        </is>
+      </c>
+      <c r="T256" s="2" t="inlineStr"/>
+      <c r="U256" s="2" t="inlineStr"/>
+      <c r="V256" s="2" t="inlineStr"/>
+      <c r="W256" s="2" t="inlineStr">
+        <is>
+          <t>Rossen Tkatchenko</t>
+        </is>
+      </c>
+      <c r="X256" s="2" t="inlineStr">
+        <is>
+          <t>Ambassador</t>
+        </is>
+      </c>
+      <c r="Y256" s="2" t="inlineStr"/>
+      <c r="Z256" s="2" t="inlineStr"/>
+      <c r="AA256" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rossent/</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>Mátrai Borok Háza</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>Mátrai Borok Háza</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>28538</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>Gyöngyös</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>North Hungary</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>16 Mátrai út</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>https://matraiborokhaza.hu</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr"/>
+      <c r="K257" s="2" t="inlineStr"/>
+      <c r="L257" s="2" t="inlineStr"/>
+      <c r="M257" s="2" t="inlineStr"/>
+      <c r="N257" s="2" t="inlineStr">
+        <is>
+          <t>info@matraiborokhaza.hu</t>
+        </is>
+      </c>
+      <c r="O257" s="2" t="inlineStr"/>
+      <c r="P257" s="2" t="inlineStr"/>
+      <c r="Q257" s="2" t="inlineStr"/>
+      <c r="R257" s="2" t="inlineStr"/>
+      <c r="S257" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/matraiborokhaza/</t>
+        </is>
+      </c>
+      <c r="T257" s="2" t="inlineStr"/>
+      <c r="U257" s="2" t="inlineStr"/>
+      <c r="V257" s="2" t="inlineStr"/>
+      <c r="W257" s="2" t="inlineStr"/>
+      <c r="X257" s="2" t="inlineStr"/>
+      <c r="Y257" s="2" t="inlineStr"/>
+      <c r="Z257" s="2" t="inlineStr"/>
+      <c r="AA257" s="2" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>7867</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>2 Szőlőkert köz</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr"/>
+      <c r="K258" s="2" t="inlineStr"/>
+      <c r="L258" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M258" s="2" t="inlineStr"/>
+      <c r="N258" s="2" t="inlineStr">
+        <is>
+          <t>webshop@borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="O258" s="2" t="inlineStr"/>
+      <c r="P258" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q258" s="2" t="inlineStr">
+        <is>
+          <t>23316564242</t>
+        </is>
+      </c>
+      <c r="R258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/veritas-borkeresked%C3%A9s-www-borkereskedes-hu/</t>
+        </is>
+      </c>
+      <c r="S258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/veritasborkereskedes/</t>
+        </is>
+      </c>
+      <c r="T258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veritas_borkereskedes/</t>
+        </is>
+      </c>
+      <c r="U258" s="2" t="inlineStr"/>
+      <c r="V258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCeGWTJE4hTW-0GbB1HK3yMw</t>
+        </is>
+      </c>
+      <c r="W258" s="2" t="inlineStr">
+        <is>
+          <t>Dezső Diószegi</t>
+        </is>
+      </c>
+      <c r="X258" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y258" s="2" t="inlineStr"/>
+      <c r="Z258" s="2" t="inlineStr"/>
+      <c r="AA258" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dezs%C5%91-di%C3%B3szegi-81023b3b/?originalSubdomain=hu</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>7867</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>2 Szőlőkert köz</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr"/>
+      <c r="K259" s="2" t="inlineStr"/>
+      <c r="L259" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M259" s="2" t="inlineStr"/>
+      <c r="N259" s="2" t="inlineStr">
+        <is>
+          <t>webshop@borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="O259" s="2" t="inlineStr"/>
+      <c r="P259" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q259" s="2" t="inlineStr">
+        <is>
+          <t>23316564242</t>
+        </is>
+      </c>
+      <c r="R259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/veritas-borkeresked%C3%A9s-www-borkereskedes-hu/</t>
+        </is>
+      </c>
+      <c r="S259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/veritasborkereskedes/</t>
+        </is>
+      </c>
+      <c r="T259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veritas_borkereskedes/</t>
+        </is>
+      </c>
+      <c r="U259" s="2" t="inlineStr"/>
+      <c r="V259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCeGWTJE4hTW-0GbB1HK3yMw</t>
+        </is>
+      </c>
+      <c r="W259" s="2" t="inlineStr">
+        <is>
+          <t>Tibor Kovács</t>
+        </is>
+      </c>
+      <c r="X259" s="2" t="inlineStr">
+        <is>
+          <t>International Wine Advisor</t>
+        </is>
+      </c>
+      <c r="Y259" s="2" t="inlineStr"/>
+      <c r="Z259" s="2" t="inlineStr"/>
+      <c r="AA259" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tibor-kov%C3%A1cs-a78026164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>Bormánia Kereskedelmi Kft.</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>Bormánia Kereskedelmi Kft.</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>24149</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>Dunakeszi</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>89 Fő út</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>2120</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>https://bormania.hu</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr"/>
+      <c r="K260" s="2" t="inlineStr"/>
+      <c r="L260" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M260" s="2" t="inlineStr"/>
+      <c r="N260" s="2" t="inlineStr">
+        <is>
+          <t>info@bormania.hu</t>
+        </is>
+      </c>
+      <c r="O260" s="2" t="inlineStr">
+        <is>
+          <t>+36 27 739 223</t>
+        </is>
+      </c>
+      <c r="P260" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q260" s="2" t="inlineStr">
+        <is>
+          <t>11981330213</t>
+        </is>
+      </c>
+      <c r="R260" s="2" t="inlineStr"/>
+      <c r="S260" s="2" t="inlineStr"/>
+      <c r="T260" s="2" t="inlineStr"/>
+      <c r="U260" s="2" t="inlineStr"/>
+      <c r="V260" s="2" t="inlineStr"/>
+      <c r="W260" s="2" t="inlineStr">
+        <is>
+          <t>Kiss Zsolt</t>
+        </is>
+      </c>
+      <c r="X260" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y260" s="2" t="inlineStr"/>
+      <c r="Z260" s="2" t="inlineStr"/>
+      <c r="AA260" s="2" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>Selection.hu Kft.</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>Selection.hu Kft.</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>7857</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>91 Lajos utca</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>https://selection.hu</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr"/>
+      <c r="K261" s="2" t="inlineStr"/>
+      <c r="L261" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M261" s="2" t="inlineStr"/>
+      <c r="N261" s="2" t="inlineStr">
+        <is>
+          <t>info@selection.hu</t>
+        </is>
+      </c>
+      <c r="O261" s="2" t="inlineStr">
+        <is>
+          <t>+36 1 439 1902</t>
+        </is>
+      </c>
+      <c r="P261" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q261" s="2" t="inlineStr">
+        <is>
+          <t>27104750241</t>
+        </is>
+      </c>
+      <c r="R261" s="2" t="inlineStr"/>
+      <c r="S261" s="2" t="inlineStr"/>
+      <c r="T261" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/selection_hu/</t>
+        </is>
+      </c>
+      <c r="U261" s="2" t="inlineStr"/>
+      <c r="V261" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@selectionhu/</t>
+        </is>
+      </c>
+      <c r="W261" s="2" t="inlineStr">
+        <is>
+          <t>Tamás Lakatos</t>
+        </is>
+      </c>
+      <c r="X261" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y261" s="2" t="inlineStr"/>
+      <c r="Z261" s="2" t="inlineStr"/>
+      <c r="AA261" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_Hungary.xlsx
+++ b/BWI/bestwine_output/bestwine_Hungary.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA261"/>
+  <dimension ref="A1:AA268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -27913,6 +27913,689 @@
       <c r="Z261" s="2" t="inlineStr"/>
       <c r="AA261" s="2" t="inlineStr"/>
     </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>Wine Mission Kft</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>Wine Mission Kft</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>35601</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>37 Nándorfejérvári út</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>1116</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>https://winemission.hu</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr"/>
+      <c r="K262" s="2" t="inlineStr"/>
+      <c r="L262" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M262" s="2" t="inlineStr"/>
+      <c r="N262" s="2" t="inlineStr">
+        <is>
+          <t>info@winemission.hu</t>
+        </is>
+      </c>
+      <c r="O262" s="2" t="inlineStr"/>
+      <c r="P262" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q262" s="2" t="inlineStr">
+        <is>
+          <t>24270661213</t>
+        </is>
+      </c>
+      <c r="R262" s="2" t="inlineStr"/>
+      <c r="S262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/winemission/</t>
+        </is>
+      </c>
+      <c r="T262" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/wine_mission_hungary</t>
+        </is>
+      </c>
+      <c r="U262" s="2" t="inlineStr"/>
+      <c r="V262" s="2" t="inlineStr"/>
+      <c r="W262" s="2" t="inlineStr">
+        <is>
+          <t>Viktor Farkas</t>
+        </is>
+      </c>
+      <c r="X262" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y262" s="2" t="inlineStr"/>
+      <c r="Z262" s="2" t="inlineStr"/>
+      <c r="AA262" s="2" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>Bormental Doktor Korlátolt Felelosségu Társaság</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>Bormental Doktor Korlátolt Felelosségu Társaság</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>29986</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>5-7 Derék utca</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>1016</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>https://bolgarborok.hu</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr"/>
+      <c r="K263" s="2" t="inlineStr"/>
+      <c r="L263" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M263" s="2" t="inlineStr"/>
+      <c r="N263" s="2" t="inlineStr">
+        <is>
+          <t>ambassador@bolgarborok.hu</t>
+        </is>
+      </c>
+      <c r="O263" s="2" t="inlineStr"/>
+      <c r="P263" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q263" s="2" t="inlineStr">
+        <is>
+          <t>22614546241</t>
+        </is>
+      </c>
+      <c r="R263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/bulgarian-wine-embassy/</t>
+        </is>
+      </c>
+      <c r="S263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/bolgarborok/</t>
+        </is>
+      </c>
+      <c r="T263" s="2" t="inlineStr"/>
+      <c r="U263" s="2" t="inlineStr"/>
+      <c r="V263" s="2" t="inlineStr"/>
+      <c r="W263" s="2" t="inlineStr">
+        <is>
+          <t>Rossen Tkatchenko</t>
+        </is>
+      </c>
+      <c r="X263" s="2" t="inlineStr">
+        <is>
+          <t>Ambassador</t>
+        </is>
+      </c>
+      <c r="Y263" s="2" t="inlineStr"/>
+      <c r="Z263" s="2" t="inlineStr"/>
+      <c r="AA263" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/rossent/</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>Mátrai Borok Háza</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>Mátrai Borok Háza</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>28538</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>Gyöngyös</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>North Hungary</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>16 Mátrai út</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>3200</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>https://matraiborokhaza.hu</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr"/>
+      <c r="K264" s="2" t="inlineStr"/>
+      <c r="L264" s="2" t="inlineStr"/>
+      <c r="M264" s="2" t="inlineStr"/>
+      <c r="N264" s="2" t="inlineStr">
+        <is>
+          <t>info@matraiborokhaza.hu</t>
+        </is>
+      </c>
+      <c r="O264" s="2" t="inlineStr"/>
+      <c r="P264" s="2" t="inlineStr"/>
+      <c r="Q264" s="2" t="inlineStr"/>
+      <c r="R264" s="2" t="inlineStr"/>
+      <c r="S264" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/matraiborokhaza/</t>
+        </is>
+      </c>
+      <c r="T264" s="2" t="inlineStr"/>
+      <c r="U264" s="2" t="inlineStr"/>
+      <c r="V264" s="2" t="inlineStr"/>
+      <c r="W264" s="2" t="inlineStr"/>
+      <c r="X264" s="2" t="inlineStr"/>
+      <c r="Y264" s="2" t="inlineStr"/>
+      <c r="Z264" s="2" t="inlineStr"/>
+      <c r="AA264" s="2" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>7867</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>2 Szőlőkert köz</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr"/>
+      <c r="K265" s="2" t="inlineStr"/>
+      <c r="L265" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M265" s="2" t="inlineStr"/>
+      <c r="N265" s="2" t="inlineStr">
+        <is>
+          <t>webshop@borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="O265" s="2" t="inlineStr"/>
+      <c r="P265" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q265" s="2" t="inlineStr">
+        <is>
+          <t>23316564242</t>
+        </is>
+      </c>
+      <c r="R265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/veritas-borkeresked%C3%A9s-www-borkereskedes-hu/</t>
+        </is>
+      </c>
+      <c r="S265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/veritasborkereskedes/</t>
+        </is>
+      </c>
+      <c r="T265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veritas_borkereskedes/</t>
+        </is>
+      </c>
+      <c r="U265" s="2" t="inlineStr"/>
+      <c r="V265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCeGWTJE4hTW-0GbB1HK3yMw</t>
+        </is>
+      </c>
+      <c r="W265" s="2" t="inlineStr">
+        <is>
+          <t>Dezső Diószegi</t>
+        </is>
+      </c>
+      <c r="X265" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y265" s="2" t="inlineStr"/>
+      <c r="Z265" s="2" t="inlineStr"/>
+      <c r="AA265" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dezs%C5%91-di%C3%B3szegi-81023b3b/?originalSubdomain=hu</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>Világ Borai Kft.</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>7867</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>2 Szőlőkert köz</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>1033</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr"/>
+      <c r="K266" s="2" t="inlineStr"/>
+      <c r="L266" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="inlineStr"/>
+      <c r="N266" s="2" t="inlineStr">
+        <is>
+          <t>webshop@borkereskedes.hu</t>
+        </is>
+      </c>
+      <c r="O266" s="2" t="inlineStr"/>
+      <c r="P266" s="2" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="Q266" s="2" t="inlineStr">
+        <is>
+          <t>23316564242</t>
+        </is>
+      </c>
+      <c r="R266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/veritas-borkeresked%C3%A9s-www-borkereskedes-hu/</t>
+        </is>
+      </c>
+      <c r="S266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/veritasborkereskedes/</t>
+        </is>
+      </c>
+      <c r="T266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/veritas_borkereskedes/</t>
+        </is>
+      </c>
+      <c r="U266" s="2" t="inlineStr"/>
+      <c r="V266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCeGWTJE4hTW-0GbB1HK3yMw</t>
+        </is>
+      </c>
+      <c r="W266" s="2" t="inlineStr">
+        <is>
+          <t>Tibor Kovács</t>
+        </is>
+      </c>
+      <c r="X266" s="2" t="inlineStr">
+        <is>
+          <t>International Wine Advisor</t>
+        </is>
+      </c>
+      <c r="Y266" s="2" t="inlineStr"/>
+      <c r="Z266" s="2" t="inlineStr"/>
+      <c r="AA266" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tibor-kov%C3%A1cs-a78026164/</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>Bormánia Kereskedelmi Kft.</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>Bormánia Kereskedelmi Kft.</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>24149</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>Dunakeszi</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>89 Fő út</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>2120</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>https://bormania.hu</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr"/>
+      <c r="K267" s="2" t="inlineStr"/>
+      <c r="L267" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M267" s="2" t="inlineStr"/>
+      <c r="N267" s="2" t="inlineStr">
+        <is>
+          <t>info@bormania.hu</t>
+        </is>
+      </c>
+      <c r="O267" s="2" t="inlineStr">
+        <is>
+          <t>+36 27 739 223</t>
+        </is>
+      </c>
+      <c r="P267" s="2" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="Q267" s="2" t="inlineStr">
+        <is>
+          <t>11981330213</t>
+        </is>
+      </c>
+      <c r="R267" s="2" t="inlineStr"/>
+      <c r="S267" s="2" t="inlineStr"/>
+      <c r="T267" s="2" t="inlineStr"/>
+      <c r="U267" s="2" t="inlineStr"/>
+      <c r="V267" s="2" t="inlineStr"/>
+      <c r="W267" s="2" t="inlineStr">
+        <is>
+          <t>Kiss Zsolt</t>
+        </is>
+      </c>
+      <c r="X267" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y267" s="2" t="inlineStr"/>
+      <c r="Z267" s="2" t="inlineStr"/>
+      <c r="AA267" s="2" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
+        <is>
+          <t>Selection.hu Kft.</t>
+        </is>
+      </c>
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>Selection.hu Kft.</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>7857</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
+        <is>
+          <t>Hungary</t>
+        </is>
+      </c>
+      <c r="E268" s="2" t="inlineStr">
+        <is>
+          <t>Budapest</t>
+        </is>
+      </c>
+      <c r="F268" s="2" t="inlineStr">
+        <is>
+          <t>Central Hungary</t>
+        </is>
+      </c>
+      <c r="G268" s="2" t="inlineStr">
+        <is>
+          <t>91 Lajos utca</t>
+        </is>
+      </c>
+      <c r="H268" s="2" t="inlineStr">
+        <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="I268" s="2" t="inlineStr">
+        <is>
+          <t>https://selection.hu</t>
+        </is>
+      </c>
+      <c r="J268" s="2" t="inlineStr"/>
+      <c r="K268" s="2" t="inlineStr"/>
+      <c r="L268" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M268" s="2" t="inlineStr"/>
+      <c r="N268" s="2" t="inlineStr">
+        <is>
+          <t>info@selection.hu</t>
+        </is>
+      </c>
+      <c r="O268" s="2" t="inlineStr">
+        <is>
+          <t>+36 1 439 1902</t>
+        </is>
+      </c>
+      <c r="P268" s="2" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="Q268" s="2" t="inlineStr">
+        <is>
+          <t>27104750241</t>
+        </is>
+      </c>
+      <c r="R268" s="2" t="inlineStr"/>
+      <c r="S268" s="2" t="inlineStr"/>
+      <c r="T268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/selection_hu/</t>
+        </is>
+      </c>
+      <c r="U268" s="2" t="inlineStr"/>
+      <c r="V268" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@selectionhu/</t>
+        </is>
+      </c>
+      <c r="W268" s="2" t="inlineStr">
+        <is>
+          <t>Tamás Lakatos</t>
+        </is>
+      </c>
+      <c r="X268" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y268" s="2" t="inlineStr"/>
+      <c r="Z268" s="2" t="inlineStr"/>
+      <c r="AA268" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
